--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPY.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dietrichhadler\Documents\DataMpFunLab\Workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUHad\Documents\DataXlCalcNet\DataExamples\MainExamples\Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384D0610-7777-43A0-8C1D-420FAC7C4F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CA7D82-63F0-4F87-ACC2-1917532FA534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18788" windowHeight="20055" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1410" yWindow="1410" windowWidth="28140" windowHeight="14603" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralInfo" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,17 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -403,7 +414,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -419,9 +430,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -459,7 +470,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -565,7 +576,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -707,7 +718,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -716,7 +727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.86328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
@@ -734,7 +745,7 @@
       </c>
       <c r="B3" t="str">
         <f>_xll.CPY_0("result  = platform.platform()")</f>
-        <v>Windows-10-10.0.19045-SP0</v>
+        <v>Windows-11-10.0.26200-SP0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -743,7 +754,7 @@
       </c>
       <c r="B4" t="str">
         <f>_xll.CPY_0("result =  platform.processor()")</f>
-        <v>Intel64 Family 6 Model 60 Stepping 3, GenuineIntel</v>
+        <v>Intel64 Family 6 Model 165 Stepping 5, GenuineIntel</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -752,7 +763,7 @@
       </c>
       <c r="B5" t="str">
         <f>_xll.CPY_0("result = platform.python_compiler()")</f>
-        <v>MSC v.1928 64 bit (AMD64)</v>
+        <v>MSC v.1942 64 bit (AMD64)</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -761,7 +772,7 @@
       </c>
       <c r="B6" t="str">
         <f>_xll.CPY_0("result = platform.python_version()")</f>
-        <v>3.8.10</v>
+        <v>3.12.8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -779,7 +790,7 @@
       </c>
       <c r="B8" t="str">
         <f>_xll.CPY_0("result = str(platform.python_build())")</f>
-        <v>('tags/v3.8.10:3d8993a', 'May  3 2021 11:48:03')</v>
+        <v>('tags/v3.12.8:2dc476b', 'Dec  3 2024 19:30:04')</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -802,7 +813,7 @@
       </c>
       <c r="B13" t="str">
         <f>_xll.CPY_0("result =  os.path.realpath(__file__);")</f>
-        <v>C:\Python38\Lib\site-packages\mpfunlab\Addin\MicrosoftExcel\socketspy.py</v>
+        <v>C:\Python312\Lib\site-packages\xlcalcnet\Addin\NET48\Bin\socketspy.py</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -820,7 +831,7 @@
       </c>
       <c r="B15" t="str">
         <f>_xll.CPY_0("result = str(os.environ)")</f>
-        <v>$file:$</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -829,7 +840,7 @@
       </c>
       <c r="B16" t="str">
         <f>_xll.CPY_0("result  = os.getcwd()")</f>
-        <v>C:\Users\dietrichhadler\Desktop\Stats32\Work</v>
+        <v>C:\Python312</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -838,7 +849,7 @@
       </c>
       <c r="B17" t="str">
         <f>_xll.CPY_0("result =  os.getenv('APPDATA')")</f>
-        <v>C:\Users\dietrichhadler\AppData\Roaming</v>
+        <v>C:\Users\DUHad\AppData\Roaming</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -847,7 +858,7 @@
       </c>
       <c r="B18" t="str">
         <f>_xll.CPY_0("result = str(os.get_exec_path())")</f>
-        <v>$file:$</v>
+        <v>['C:\\Program Files\\Parallels\\Parallels Tools\\Applications', 'C:\\WINDOWS\\system32', 'C:\\WINDOWS', 'C:\\WINDOWS\\System32\\Wbem', 'C:\\WINDOWS\\System32\\WindowsPowerShell\\v1.0\\', 'C:\\WINDOWS\\System32\\OpenSSH\\', 'C:\\Users\\DUHad\\AppData\\Local\\Microsoft\\WindowsApps', '']</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="13.15" x14ac:dyDescent="0.4">
@@ -860,8 +871,8 @@
         <v>16</v>
       </c>
       <c r="B22" t="str">
-        <f>_xll.CPY_0("result = str(sys.executable)")</f>
-        <v>C:\Python38\python.exe</v>
+        <f>_xll.CPY_0("result  = str(sys.executable)")</f>
+        <v>C:\Python312\python.exe</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -870,7 +881,7 @@
       </c>
       <c r="B23" t="str">
         <f>_xll.CPY_0("result = str(sys.prefix)")</f>
-        <v>C:\Python38</v>
+        <v>C:\Python312</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
@@ -879,7 +890,7 @@
       </c>
       <c r="B24" t="str">
         <f>_xll.CPY_0("result  =  str(sys.path);")</f>
-        <v>['C:\\Python38\\Lib\\site-packages\\mpfebnet\\Addin\\MicrosoftExcel', 'C:\\Python38\\python38.zip', 'C:\\Python38\\DLLs', 'C:\\Python38\\lib', 'C:\\Python38', 'C:\\Python38\\lib\\site-packages', 'C:\\Python38\\lib\\site-packages\\win32', 'C:\\Python38\\lib\\site-packages\\win32\\lib', 'C:\\Python38\\lib\\site-packages\\Pythonwin']</v>
+        <v>['C:\\Users\\DUHad\\Documents\\DataXlCalcNet', 'C:\\Python312\\Lib\\site-packages\\xlcalcnet\\Addin\\NET48\\Bin', 'C:\\Python312\\python312.zip', 'C:\\Python312\\DLLs', 'C:\\Python312\\Lib', 'C:\\Python312', 'C:\\Python312\\Lib\\site-packages', 'C:\\Windows\\Microsoft.NET\\Framework64\\v4.0.30319\\']</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -888,7 +899,7 @@
       </c>
       <c r="B25" t="str">
         <f>_xll.CPY_0("result = str(sys.implementation)")</f>
-        <v>namespace(cache_tag='cpython-38', hexversion=50858736, name='cpython', version=sys.version_info(major=3, minor=8, micro=10, releaselevel='final', serial=0))</v>
+        <v>namespace(name='cpython', cache_tag='cpython-312', version=sys.version_info(major=3, minor=12, micro=8, releaselevel='final', serial=0), hexversion=51120368)</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
@@ -906,7 +917,7 @@
       </c>
       <c r="B27" t="str">
         <f>_xll.CPY_0("result = str(sys.version)")</f>
-        <v>3.8.10 (tags/v3.8.10:3d8993a, May  3 2021, 11:48:03) [MSC v.1928 64 bit (AMD64)]</v>
+        <v>3.12.8 (tags/v3.12.8:2dc476b, Dec  3 2024, 19:30:04) [MSC v.1942 64 bit (AMD64)]</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -924,7 +935,7 @@
       </c>
       <c r="B29" t="str">
         <f>_xll.CPY_0("result  = str(sys.version_info)")</f>
-        <v>sys.version_info(major=3, minor=8, micro=10, releaselevel='final', serial=0)</v>
+        <v>sys.version_info(major=3, minor=12, micro=8, releaselevel='final', serial=0)</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="13.15" x14ac:dyDescent="0.4">
@@ -1037,7 +1048,7 @@
       </c>
       <c r="B46" t="str">
         <f>_xll.CPY_0("result =  os.path.dirname(str(sys.executable))")</f>
-        <v>C:\Python38</v>
+        <v>C:\Python312</v>
       </c>
       <c r="C46" s="2"/>
     </row>
@@ -1053,7 +1064,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.265625" customWidth="1"/>
     <col min="2" max="2" width="44.6640625" customWidth="1"/>
@@ -1083,9 +1094,9 @@
       <c r="A4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" t="e">
         <f>_xll.CPY_0("result = float('NaN')")</f>
-        <v>nan</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1194,7 +1205,7 @@
       <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B15">
         <f>_xll.CPY_1("result = math.factorial(int(P1))",C15)</f>
         <v>5040</v>
       </c>
@@ -1296,9 +1307,9 @@
       <c r="A24" t="s">
         <v>62</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B24" t="b">
         <f>_xll.CPY_1("result = math.isinf(float(P1))",C24)</f>
-        <v>False</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <v>34346</v>
@@ -1310,7 +1321,7 @@
       </c>
       <c r="B25" t="str">
         <f>_xll.CPY_1("result = math.isnan(float(P1))",B4)</f>
-        <v>True</v>
+        <v>Exception: name 'P1' is not defined</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1326,9 +1337,9 @@
       <c r="A27" t="s">
         <v>65</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B27" t="b">
         <f>_xll.CPY_1("result = math.isnan(float(P1))",C27)</f>
-        <v>False</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>34346</v>
@@ -1415,7 +1426,7 @@
       </c>
       <c r="B34">
         <f>_xll.CPY_1("result = math.expm1(P1)",C34)</f>
-        <v>1.0000050000166667E-5</v>
+        <v>1.0000050000166668E-5</v>
       </c>
       <c r="C34">
         <v>1.0000000000000001E-5</v>
@@ -1481,10 +1492,10 @@
       </c>
       <c r="B39">
         <f>_xll.CPY_1("result = math.log10(P1)",C39)</f>
-        <v>0.4945719842301986</v>
+        <v>1.0914910942679512</v>
       </c>
       <c r="C39">
-        <v>3.1230000000000002</v>
+        <v>12.345000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -1730,7 +1741,7 @@
       </c>
       <c r="B59">
         <f>_xll.CPY_1("result = math.erfc(P1)",C59)</f>
-        <v>1.0027064684353403E-5</v>
+        <v>1.0027064684353404E-5</v>
       </c>
       <c r="C59">
         <v>3.1230000000000002</v>
@@ -1769,7 +1780,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:G48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.73046875" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
@@ -1781,54 +1792,54 @@
         <v>100</v>
       </c>
       <c r="B3" t="str">
-        <f>_xll.CPY_0("result   = str(sys.path)")</f>
-        <v>['C:\\Python38\\Lib\\site-packages\\mpfebnet\\Addin\\MicrosoftExcel', 'C:\\Python38\\python38.zip', 'C:\\Python38\\DLLs', 'C:\\Python38\\lib', 'C:\\Python38', 'C:\\Python38\\lib\\site-packages', 'C:\\Python38\\lib\\site-packages\\win32', 'C:\\Python38\\lib\\site-packages\\win32\\lib', 'C:\\Python38\\lib\\site-packages\\Pythonwin']</v>
+        <f>_xll.CPY_0("result  = str(sys.path)")</f>
+        <v>['C:\\Users\\DUHad\\Documents\\DataXlCalcNet', 'C:\\Python312\\Lib\\site-packages\\xlcalcnet\\Addin\\NET48\\Bin', 'C:\\Python312\\python312.zip', 'C:\\Python312\\DLLs', 'C:\\Python312\\Lib', 'C:\\Python312', 'C:\\Python312\\Lib\\site-packages', 'C:\\Windows\\Microsoft.NET\\Framework64\\v4.0.30319\\']</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="str">
-        <f t="array" ref="A4:A14">_xll.CPY_0("result =list(zip(sys.path))")</f>
-        <v>C:\Python38\Lib\site-packages\mpfebnet\Addin\MicrosoftExcel</v>
+        <f t="array" ref="A4:A14">_xll.CPY_0("result  =list(zip(sys.path))")</f>
+        <v>C:\Users\DUHad\Documents\DataXlCalcNet</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
-        <v>C:\Python38\python38.zip</v>
+        <v>C:\Python312\Lib\site-packages\xlcalcnet\Addin\NET48\Bin</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
-        <v>C:\Python38\DLLs</v>
+        <v>C:\Python312\python312.zip</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
-        <v>C:\Python38\lib</v>
+        <v>C:\Python312\DLLs</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
-        <v>C:\Python38</v>
+        <v>C:\Python312\Lib</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
-        <v>C:\Python38\lib\site-packages</v>
+        <v>C:\Python312</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
-        <v>C:\Python38\lib\site-packages\win32</v>
+        <v>C:\Python312\Lib\site-packages</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
-        <v>C:\Python38\lib\site-packages\win32\lib</v>
+        <v>C:\Windows\Microsoft.NET\Framework64\v4.0.30319\</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="str">
-        <v>C:\Python38\lib\site-packages\Pythonwin</v>
+      <c r="A12" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1843,7 +1854,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
-        <f>_xll.CPY_0("result = rxc(list(zip(['1','2','3'])))")</f>
+        <f>_xll.CPY_0("result  = rxc(list(zip(['1','2','3'])))")</f>
         <v>Exception: name 'rxc' is not defined</v>
       </c>
     </row>
@@ -1865,7 +1876,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
-        <f>_xll.CPY_0("result = rxc(['1','2','3'])")</f>
+        <f>_xll.CPY_0("result  = rxc(['1','2','3'])")</f>
         <v>Exception: name 'rxc' is not defined</v>
       </c>
     </row>
@@ -2023,7 +2034,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:C18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.53125" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" customWidth="1"/>
@@ -2054,7 +2065,7 @@
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>_xll.CPY_0("from mpfunlab import mpm $n  mpm.dps=50 $n result  = str(mpm.sqrt(2))")</f>
-        <v>1.4142135623730950488016887242096980785696718753769</v>
+        <v>Exception: No module named 'mpfunlab'</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -2065,7 +2076,7 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>_xll.CPY_0("from mpfunlab import mpa, mpm $n  mpm.dps=35 $n res  = mpm.student_t_1sample_test(n = [10, 24, 30], mu0 = 1.0, mean = [4.5,4.6], std = [1,2,3,4], alpha=0.015)" &amp;  "$n mpa.table(res, r'C:\Temp\Temp.py', 'Student t-test, 1 sample: p-values and confidence intervals')  $n  result = 'Table Done' ")</f>
-        <v>Table Done</v>
+        <v>Exception: No module named 'mpfunlab'</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -2076,7 +2087,7 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>_xll.CPY_0("from mpfunlab import mpa $n   import matplotlib.pyplot as plt $n import numpy  as np $n  t = np.arange(0.0, 2.0, 0.01) $n s = 1 + np.sin(2 * np.pi * t) $n fig, ax = plt.subplots() $n ax.plot(t, s)" &amp; " $n ax.set(xlabel='time (s)', ylabel='voltage (mV)', title='About as simple as it gets, folks') $n ax.grid() " &amp;  "$n mpa.plot(fig, r'C:\Temp\Temp.py', 'Simpleplot3')  $n  result = 'Graphics Done' ")</f>
-        <v>Graphics Done</v>
+        <v>Exception: No module named 'mpfunlab'</v>
       </c>
     </row>
   </sheetData>
@@ -2088,7 +2099,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A3:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
